--- a/astro-site/public/dl/restaurant-checklist-templates/03-restaurant-manager-checklist.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/03-restaurant-manager-checklist.xlsx
@@ -870,7 +870,7 @@
     <row r="34" ht="31" customHeight="1">
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
     <row r="38" ht="47" customHeight="1">
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>▸ You are in 03-restaurant-manager-checklist.xlsx: it is one MORE layer, not a repeat — the frame of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
+          <t>▸ You are in 03-restaurant-manager-checklist.xlsx: it is one MORE layer, not a repeat — the backbone of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Review delivery slips still waiting for invoices</t>
+          <t>Match delivery invoices and packing slips to vendor statements; chase missing credits</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>File this month's time-clock records (FLSA: time cards 2 years, payroll 3 years)</t>
+          <t>File this month's time-clock records (FLSA minimum: time cards 2 years, payroll 3 years; some states require longer, e.g. NY 6)</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Process payroll, including tips, overtime and bonuses</t>
+          <t>Reconcile the month's payroll runs (weekly or biweekly, per your state's pay-frequency law): tips, overtime, bonuses</t>
         </is>
       </c>
       <c r="C18" s="36" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
